--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hideaway\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B36521-5B5B-4E12-B8EC-E2F5AC42AA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="77">
   <si>
     <t>Employee_ID</t>
   </si>
@@ -227,13 +233,31 @@
   </si>
   <si>
     <t>Greivin Guido - Alimentos Cocina</t>
+  </si>
+  <si>
+    <t>Deyvi Martinez Ramirez</t>
+  </si>
+  <si>
+    <t>Jose Andres Mora Rodriguez</t>
+  </si>
+  <si>
+    <t>Yahaira Herrera Segura</t>
+  </si>
+  <si>
+    <t>Manuel Andres Sanchez Lopez</t>
+  </si>
+  <si>
+    <t>Kendall Jiménez Reyes</t>
+  </si>
+  <si>
+    <t>Jean Carlos Matamoros</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,13 +294,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -314,7 +346,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -348,6 +380,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -382,9 +415,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -557,11 +591,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C71"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -572,7 +609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -583,7 +620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -594,7 +631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>5</v>
       </c>
@@ -605,7 +642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>9</v>
       </c>
@@ -616,7 +653,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>10</v>
       </c>
@@ -627,7 +664,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>11</v>
       </c>
@@ -638,7 +675,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>12</v>
       </c>
@@ -649,7 +686,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>15</v>
       </c>
@@ -660,7 +697,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>17</v>
       </c>
@@ -671,7 +708,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>19</v>
       </c>
@@ -682,7 +719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>20</v>
       </c>
@@ -693,7 +730,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>21</v>
       </c>
@@ -704,7 +741,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>22</v>
       </c>
@@ -715,7 +752,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>24</v>
       </c>
@@ -726,7 +763,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>25</v>
       </c>
@@ -737,7 +774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26</v>
       </c>
@@ -748,7 +785,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>32</v>
       </c>
@@ -759,7 +796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>33</v>
       </c>
@@ -770,7 +807,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>34</v>
       </c>
@@ -781,7 +818,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>35</v>
       </c>
@@ -792,7 +829,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>36</v>
       </c>
@@ -803,7 +840,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>37</v>
       </c>
@@ -814,7 +851,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>38</v>
       </c>
@@ -825,7 +862,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>39</v>
       </c>
@@ -836,7 +873,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>40</v>
       </c>
@@ -847,7 +884,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>41</v>
       </c>
@@ -858,7 +895,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>42</v>
       </c>
@@ -869,7 +906,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>43</v>
       </c>
@@ -880,7 +917,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>46</v>
       </c>
@@ -891,7 +928,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>47</v>
       </c>
@@ -902,7 +939,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>48</v>
       </c>
@@ -913,7 +950,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>50</v>
       </c>
@@ -924,7 +961,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>54</v>
       </c>
@@ -935,7 +972,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>55</v>
       </c>
@@ -946,7 +983,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>56</v>
       </c>
@@ -957,7 +994,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>62</v>
       </c>
@@ -968,7 +1005,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>65</v>
       </c>
@@ -979,7 +1016,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>70</v>
       </c>
@@ -990,7 +1027,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>73</v>
       </c>
@@ -1001,7 +1038,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>76</v>
       </c>
@@ -1012,7 +1049,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>77</v>
       </c>
@@ -1023,7 +1060,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>80</v>
       </c>
@@ -1034,7 +1071,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>81</v>
       </c>
@@ -1045,7 +1082,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>84</v>
       </c>
@@ -1056,7 +1093,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>88</v>
       </c>
@@ -1067,7 +1104,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>91</v>
       </c>
@@ -1078,7 +1115,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>94</v>
       </c>
@@ -1089,7 +1126,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>102</v>
       </c>
@@ -1100,7 +1137,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>103</v>
       </c>
@@ -1111,7 +1148,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>108</v>
       </c>
@@ -1122,7 +1159,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>111</v>
       </c>
@@ -1133,7 +1170,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>112</v>
       </c>
@@ -1144,7 +1181,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>114</v>
       </c>
@@ -1155,7 +1192,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>117</v>
       </c>
@@ -1166,7 +1203,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>119</v>
       </c>
@@ -1177,7 +1214,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>121</v>
       </c>
@@ -1188,7 +1225,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>122</v>
       </c>
@@ -1199,7 +1236,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>126</v>
       </c>
@@ -1210,7 +1247,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>128</v>
       </c>
@@ -1221,7 +1258,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>129</v>
       </c>
@@ -1232,7 +1269,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>135</v>
       </c>
@@ -1243,7 +1280,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>138</v>
       </c>
@@ -1254,7 +1291,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>139</v>
       </c>
@@ -1265,7 +1302,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>141</v>
       </c>
@@ -1274,6 +1311,72 @@
       </c>
       <c r="C65" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>142</v>
+      </c>
+      <c r="B66" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>143</v>
+      </c>
+      <c r="B67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>144</v>
+      </c>
+      <c r="B68" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>145</v>
+      </c>
+      <c r="B69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>146</v>
+      </c>
+      <c r="B70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>147</v>
+      </c>
+      <c r="B71" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
